--- a/sheets/대금율보/검수/현천수.xlsx
+++ b/sheets/대금율보/검수/현천수.xlsx
@@ -6134,8 +6134,7 @@
         <is>
           <t xml:space="preserve">林∧
 –太ㅅ
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -6179,8 +6178,7 @@
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∧
-‹</t>
+          <t xml:space="preserve">林∧</t>
         </is>
       </c>
       <c r="S3" s="22"/>
@@ -6205,8 +6203,7 @@
         <is>
           <t xml:space="preserve">汰潢
 –
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="E4" s="22"/>
@@ -6222,8 +6219,7 @@
         <is>
           <t xml:space="preserve">林∧
 –太ㅅ
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="I4" s="22"/>
@@ -6231,8 +6227,7 @@
         <is>
           <t xml:space="preserve">太黃
 –
-太∧
-‹</t>
+太∧</t>
         </is>
       </c>
       <c r="K4" s="24"/>
@@ -6256,8 +6251,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –h
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="Q4" s="22"/>
@@ -6273,8 +6267,7 @@
         <is>
           <t xml:space="preserve">太林∧
 –
-И
-‹</t>
+И</t>
         </is>
       </c>
       <c r="U4" s="22"/>
@@ -6285,8 +6278,7 @@
         <is>
           <t xml:space="preserve">林∧
 –
-南∧
-‹</t>
+南∧</t>
         </is>
       </c>
       <c r="C5" s="22"/>
@@ -6302,8 +6294,7 @@
         <is>
           <t xml:space="preserve">林∧
 –南∧
-南I
-‹</t>
+南I</t>
         </is>
       </c>
       <c r="G5" s="22"/>
@@ -6327,8 +6318,7 @@
         <is>
           <t xml:space="preserve">林∧
 –
-南∧
-‹</t>
+南∧</t>
         </is>
       </c>
       <c r="M5" s="22"/>
@@ -6336,8 +6326,7 @@
         <is>
           <t xml:space="preserve">林∧
 –
-南∧
-‹</t>
+南∧</t>
         </is>
       </c>
       <c r="O5" s="22"/>
@@ -6351,8 +6340,7 @@
         <is>
           <t xml:space="preserve">林∧
 –南∧
-南I
-‹</t>
+南I</t>
         </is>
       </c>
       <c r="S5" s="22"/>
@@ -6462,18 +6450,13 @@
         </is>
       </c>
       <c r="G7" s="22"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H7" s="21"/>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –汰
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -6493,8 +6476,7 @@
         <is>
           <t xml:space="preserve">潢
 –㴌
-ㅣ汰潢·
-‹</t>
+ㅣ汰潢·</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
@@ -6506,11 +6488,7 @@
         </is>
       </c>
       <c r="S7" s="22"/>
-      <c r="T7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
@@ -6567,8 +6545,7 @@
         <is>
           <t xml:space="preserve">–
 –
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="O8" s="22"/>
@@ -6669,8 +6646,7 @@
       <c r="K11" s="22"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∧
-‹</t>
+          <t xml:space="preserve">潢∧</t>
         </is>
       </c>
       <c r="M11" s="22"/>
@@ -6711,8 +6687,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –林ㅅ
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -6720,8 +6695,7 @@
         <is>
           <t xml:space="preserve">林仲
 –
-林∧
-‹</t>
+林∧</t>
         </is>
       </c>
       <c r="E12" s="24"/>
@@ -6745,8 +6719,7 @@
         <is>
           <t xml:space="preserve">㳞ㅅ
 –h
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -6762,8 +6735,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –汰∧
-Z
-‹</t>
+Z</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -6771,8 +6743,7 @@
         <is>
           <t xml:space="preserve">林∧
 –太ㅅ
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -6788,8 +6759,7 @@
         <is>
           <t xml:space="preserve">潢
 –㴌
-汰ㅅ
-‹</t>
+汰ㅅ</t>
         </is>
       </c>
       <c r="U12" s="22"/>
@@ -6808,8 +6778,7 @@
         <is>
           <t xml:space="preserve">潢ㅅ
 –汰∧
-汰I
-‹</t>
+汰I</t>
         </is>
       </c>
       <c r="E13" s="22"/>
@@ -6817,8 +6786,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="G13" s="22"/>
@@ -6826,8 +6794,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="I13" s="22"/>
@@ -6841,8 +6808,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –汰∧
-汰I
-‹</t>
+汰I</t>
         </is>
       </c>
       <c r="M13" s="22"/>
@@ -6866,8 +6832,7 @@
         <is>
           <t xml:space="preserve">林∧
 –南∧
-南I
-‹</t>
+南I</t>
         </is>
       </c>
       <c r="S13" s="22"/>
@@ -6955,18 +6920,13 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B15" s="21"/>
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –淋∧
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -6998,11 +6958,7 @@
         </is>
       </c>
       <c r="M15" s="22"/>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N15" s="21"/>
       <c r="O15" s="22"/>
       <c r="P15" s="23" t="inlineStr">
         <is>
@@ -7016,8 +6972,7 @@
         <is>
           <t xml:space="preserve">–
 –汰
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="S15" s="22"/>
@@ -7193,8 +7148,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –林ㅅ
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="U19" s="22"/>
@@ -7213,8 +7167,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –林ㅅ
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K20" s="22"/>
@@ -7230,8 +7183,7 @@
         <is>
           <t xml:space="preserve">㳞
 –湳
-ㅣ淋㳞·
-‹</t>
+ㅣ淋㳞·</t>
         </is>
       </c>
       <c r="O20" s="22"/>
@@ -7247,8 +7199,7 @@
         <is>
           <t xml:space="preserve">淋㳞
 –
-淋∧
-‹</t>
+淋∧</t>
         </is>
       </c>
       <c r="S20" s="24"/>
@@ -7299,8 +7250,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="Q21" s="22"/>
@@ -7316,8 +7266,7 @@
         <is>
           <t xml:space="preserve">潢∧
 –汰∧
-汰I
-‹</t>
+汰I</t>
         </is>
       </c>
       <c r="U21" s="22"/>
@@ -7390,8 +7339,7 @@
       <c r="L23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋∧
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="M23" s="22"/>

--- a/sheets/대금율보/검수/현천수.xlsx
+++ b/sheets/대금율보/검수/현천수.xlsx
@@ -6062,32 +6062,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="18.03" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="114.29" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="341.07" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="341.07" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="341.07" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="341.07" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="341.07" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="341.07" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6574,10 +6574,10 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9">
+    <row r="9" ht="6.0" customHeight="true">
       <c r="A9" s="0"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="114.29" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
       <c r="T10" s="20"/>
       <c r="U10" s="20"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="341.07" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="341.07" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="341.07" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="341.07" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="341.07" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="341.07" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7066,10 +7066,10 @@
       </c>
       <c r="U16" s="22"/>
     </row>
-    <row r="17">
+    <row r="17" ht="6.0" customHeight="true">
       <c r="A17" s="0"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="114.29" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="20" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="341.07" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="341.07" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="341.07" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="341.07" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="341.07" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="341.07" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
@@ -7439,7 +7439,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="35"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="8" max="16383" man="1"/>
     <brk id="16" max="16383" man="1"/>
